--- a/data/trans_bre/P38A-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 5,25</t>
+          <t>-2,19; 4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,98</t>
+          <t>0,54; 7,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 7,55</t>
+          <t>-0,3; 7,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,12</t>
+          <t>-2,45; 5,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 9,56</t>
+          <t>0,62; 9,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 8,76</t>
+          <t>-0,34; 9,04</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,55</t>
+          <t>1,75; 8,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 12,46</t>
+          <t>6,77; 12,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 52,5</t>
+          <t>4,39; 53,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 10,4</t>
+          <t>2,04; 10,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 15,46</t>
+          <t>7,98; 15,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 147,43</t>
+          <t>5,33; 153,45</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,67</t>
+          <t>2,01; 8,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 11,33</t>
+          <t>4,49; 11,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 15,18</t>
+          <t>4,09; 15,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,42</t>
+          <t>2,31; 10,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 13,99</t>
+          <t>5,27; 13,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 18,91</t>
+          <t>4,64; 19,19</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,05</t>
+          <t>2,22; 8,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,49</t>
+          <t>-0,03; 6,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 8,19</t>
+          <t>-15,94; 8,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,61</t>
+          <t>2,53; 9,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,93</t>
+          <t>0,02; 7,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 10,32</t>
+          <t>-18,9; 10,45</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,03</t>
+          <t>2,69; 6,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,97</t>
+          <t>4,72; 8,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 28,77</t>
+          <t>3,27; 28,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,16</t>
+          <t>3,12; 7,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,68</t>
+          <t>5,59; 9,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 46,0</t>
+          <t>3,87; 47,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38A-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 4,65</t>
+          <t>-2,11; 4,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,65</t>
+          <t>0,99; 8,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 7,82</t>
+          <t>-0,61; 7,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 5,39</t>
+          <t>-2,35; 5,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 9,19</t>
+          <t>1,14; 9,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 9,04</t>
+          <t>-0,67; 8,39</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22,81</t>
+          <t>6,01</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,39</t>
+          <t>1,94; 8,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,77; 12,67</t>
+          <t>6,55; 12,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 53,98</t>
+          <t>2,88; 9,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 10,27</t>
+          <t>2,31; 10,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 15,84</t>
+          <t>7,72; 15,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 153,45</t>
+          <t>3,54; 12,47</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,95</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,69</t>
+          <t>1,64; 8,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,05</t>
+          <t>4,28; 11,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 15,44</t>
+          <t>3,08; 11,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,55</t>
+          <t>1,89; 10,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 13,66</t>
+          <t>4,95; 13,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 19,19</t>
+          <t>3,62; 14,35</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,11</t>
+          <t>2,37; 8,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,37</t>
+          <t>-0,16; 6,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 8,35</t>
+          <t>2,64; 10,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 9,66</t>
+          <t>2,7; 9,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,83</t>
+          <t>-0,18; 7,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 10,45</t>
+          <t>3,26; 14,02</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,59</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,04</t>
+          <t>2,72; 5,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,12</t>
+          <t>4,54; 7,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 28,16</t>
+          <t>3,9; 7,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,16</t>
+          <t>3,12; 6,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,86</t>
+          <t>5,38; 9,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 47,1</t>
+          <t>4,65; 9,71</t>
         </is>
       </c>
     </row>
